--- a/DOCS/ThingEdu_GCompris-vi_202HoatDong_YNghia_Papert_GDPT2018_NLS.xlsx
+++ b/DOCS/ThingEdu_GCompris-vi_202HoatDong_YNghia_Papert_GDPT2018_NLS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HuongDan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="202-HoatDong" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TheoNhom" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HuongDan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="202-HoatDong" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TheoNhom" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'202-HoatDong'!$A$4:$N$206</definedName>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Mười que tính bó thành một bó — một bó là một đơn vị, một que là một phần mười.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Chai nhựa có lỗ và ống hút làm tàu ngầm cartesian: bóp chai thì chìm, thả ra thì nổi.</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Thả quả bóng từ các độ cao khác nhau, bấm giờ và ghi lại — cảm nhận gia tốc trước.</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Tám cái đèn pin hoặc tám tấm bìa lật, mỗi cái một giá trị 1-2-4-8… Trẻ bật tắt để đếm.</t>
         </is>
       </c>
     </row>
@@ -2158,17 +2158,17 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Cân cho thăng bằng</t>
+          <t>Cho thuyền qua âu tàu</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>scalesboard</t>
+          <t>canal_lock</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Khoa học</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -2183,27 +2183,27 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Kéo thả các quả cân để cân thăng bằng.</t>
+          <t>Tux đang gặp khó, thuyền của bạn ấy phải qua âu tàu. Giúp Tux và tìm hiểu âu tàu hoạt động thế nào.</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Tính nhẩm, đẳng thức số học.</t>
+          <t>Hiểu âu tàu hoạt động thế nào.</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Tự nhiên và Xã hội (TH) · Khoa học · KHTN</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>NL tính toán · NL giải quyết vấn đề</t>
+          <t>NL khoa học · NL tìm hiểu tự nhiên</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số — Trẻ thử – sai – sửa trên máy, đúng mạch 'giải quyết vấn đề kỹ thuật' của miền V.</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Trẻ thử – sai – sửa trên máy, đúng mạch 'giải quyết vấn đề kỹ thuật' của miền V.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>Cân thăng bằng là mô hình vật lý của dấu bằng. Trẻ hiểu phương trình bằng tay trước khi gặp chữ x.</t>
+          <t>Một cơ cấu thật của thế giới người lớn, thu nhỏ lại vừa tay trẻ. Trẻ phải hiểu nguyên lý mới mở đúng thứ tự van.</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>Cân đĩa thật với quả cân tự làm từ đồng xu, hạt.</t>
+          <t>Âu tàu bằng hai hộp nhựa nối ống: đổ nước, mở van, xem thuyền giấy lên xuống theo mực nước.</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Học xem đồng hồ</t>
+          <t>Cân cho thăng bằng</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>clockgame</t>
+          <t>scalesboard</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Học cách xem giờ trên đồng hồ kim.</t>
+          <t>Kéo thả các quả cân để cân thăng bằng.</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>Học các đơn vị thời gian (giờ, phút và giây). Chỉnh giờ trên đồng hồ kim.</t>
+          <t>Tính nhẩm, đẳng thức số học.</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>Vi thế giới: trẻ thao tác trên một hệ có luật riêng và tự rút ra quy luật. Học các đơn vị thời gian (giờ, phút và giây). Chỉnh giờ trên đồng hồ kim.</t>
+          <t>Cân thăng bằng là mô hình vật lý của dấu bằng. Trẻ hiểu phương trình bằng tay trước khi gặp chữ x.</t>
         </is>
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>Đồng hồ giấy có kim xoay được, tự làm.</t>
+          <t>Cân đĩa thật với quả cân tự làm từ đồng xu, hạt.</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Hộp thăng bằng</t>
+          <t>Học xem đồng hồ</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>balancebox</t>
+          <t>clockgame</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Cảm ứng</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -2323,27 +2323,27 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Nghiêng hộp để đưa quả bóng tới cửa.</t>
+          <t>Học cách xem giờ trên đồng hồ kim.</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Luyện vận động tinh và đếm cơ bản.</t>
+          <t>Học các đơn vị thời gian (giờ, phút và giây). Chỉnh giờ trên đồng hồ kim.</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Tin học</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>NL tin học · NL công nghệ</t>
+          <t>NL tính toán · NL giải quyết vấn đề</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>5.1 Giải quyết vấn đề kỹ thuật — Trẻ thử – sai – sửa trên máy, đúng mạch 'giải quyết vấn đề kỹ thuật' của miền V.</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số — Trẻ thử – sai – sửa trên máy, đúng mạch 'giải quyết vấn đề kỹ thuật' của miền V.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>Có trình soạn màn chơi: trẻ chuyển từ người chơi thành người làm ra trò chơi. Đây đúng là điều Papert mong nhất ở phần mềm giáo dục.</t>
+          <t>Vi thế giới: trẻ thao tác trên một hệ có luật riêng và tự rút ra quy luật. Học các đơn vị thời gian (giờ, phút và giây). Chỉnh giờ trên đồng hồ kim.</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Mê cung nghiêng bằng bìa và bi ve.</t>
+          <t>Đồng hồ giấy có kim xoay được, tự làm.</t>
         </is>
       </c>
     </row>
@@ -2368,17 +2368,17 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Vận hành âu thuyền</t>
+          <t>Hộp thăng bằng</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>canal_lock</t>
+          <t>balancebox</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Khoa học</t>
+          <t>Cảm ứng</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2393,27 +2393,27 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Tux đang gặp khó, thuyền của bạn ấy phải qua âu thuyền. Giúp Tux và tìm hiểu âu thuyền hoạt động thế nào.</t>
+          <t>Nghiêng hộp để đưa quả bóng tới cửa.</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>Hiểu âu thuyền hoạt động thế nào.</t>
+          <t>Luyện vận động tinh và đếm cơ bản.</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>Tự nhiên và Xã hội (TH) · Khoa học · KHTN</t>
+          <t>Tin học</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>NL khoa học · NL tìm hiểu tự nhiên</t>
+          <t>NL tin học · NL công nghệ</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Trẻ thử – sai – sửa trên máy, đúng mạch 'giải quyết vấn đề kỹ thuật' của miền V.</t>
+          <t>5.1 Giải quyết vấn đề kỹ thuật — Trẻ thử – sai – sửa trên máy, đúng mạch 'giải quyết vấn đề kỹ thuật' của miền V.</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>Một cơ cấu thật của thế giới người lớn, thu nhỏ lại vừa tay trẻ. Trẻ phải hiểu nguyên lý mới mở đúng thứ tự van.</t>
+          <t>Có trình soạn màn chơi: trẻ chuyển từ người chơi thành người làm ra trò chơi. Đây đúng là điều Papert mong nhất ở phần mềm giáo dục.</t>
         </is>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Mê cung nghiêng bằng bìa và bi ve.</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Thước mét dán lên tường, trẻ dán kẹp giấy vào đúng vạch được đọc lên.</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Dải hoa văn bằng nắp chai, hạt và giấy màu dán trên băng giấy dài quanh lớp.</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Bạn A đọc dãy lệnh, bạn B bịt mắt đi theo trong lớp.</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Bạn A đọc lệnh quay trái, quay phải; bạn B bịt mắt làm theo — hướng tính theo thân mình.</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="N34" s="9" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Rổ cam, quýt thật để trẻ đếm và bốc đúng số lượng.</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Trẻ viết dãy lệnh ra thẻ giấy để bạn khác đi theo mà tới đúng chỗ.</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="N36" s="9" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Trẻ viết lệnh quay trái, quay phải ra thẻ giấy cho bạn bịt mắt đi theo.</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Thước mét dán lên tường, trẻ chỉ và đọc vạch.</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>La bàn</t>
+          <t>Vẽ bằng bánh răng</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>compass</t>
+          <t>drawing_wheels</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Dùng compa để vẽ.</t>
+          <t>Lăn bánh răng trong vòng răng để vẽ.</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Học cách vẽ đường tròn và cung tròn bằng compa.</t>
+          <t>Khám phá đường hypotrochoid và dùng chúng làm công cụ vẽ trên máy tính.</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Compa số có cả chế độ tự do lẫn mẫu để bắt chước. Hình học thành việc dựng hình chứ không phải học thuộc.</t>
+          <t>Bộ vẽ spirograph số. Trẻ đổi số răng rồi thấy hình đổi theo — quan hệ toán học hiện ra thành cái đẹp.</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Compa thật trên giấy.</t>
+          <t>Vẽ, cắt, dán trên giấy thật.</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Vẽ bằng bánh răng</t>
+          <t>Vẽ bằng compa</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>drawing_wheels</t>
+          <t>compass</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>Lăn bánh răng trong vòng răng để vẽ.</t>
+          <t>Dùng compa để vẽ.</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>Khám phá đường hypotrochoid và dùng chúng làm công cụ vẽ trên máy tính.</t>
+          <t>Học cách vẽ đường tròn và cung tròn bằng compa.</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>Bộ vẽ spirograph số. Trẻ đổi số răng rồi thấy hình đổi theo — quan hệ toán học hiện ra thành cái đẹp.</t>
+          <t>Compa số có cả chế độ tự do lẫn mẫu để bắt chước. Hình học thành việc dựng hình chứ không phải học thuộc.</t>
         </is>
       </c>
       <c r="N44" s="9" t="inlineStr">
         <is>
-          <t>Vẽ, cắt, dán trên giấy thật.</t>
+          <t>Compa thật trên giấy.</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Tính sao cho ra 24.</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Trò trượt ô xếp hình</t>
+          <t>Trò trượt xe trong bãi đỗ</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Phép trừ đặt tính dọc (có nhớ)</t>
+          <t>Phép trừ đặt tính dọc (kiểu bù trừ)</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
@@ -10908,17 +10908,17 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>Chạm đúp hoặc bấm đúp</t>
+          <t>Bắt số theo thứ tự</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>erase_2clic</t>
+          <t>planegame</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>Máy tính</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
@@ -10933,27 +10933,27 @@
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>Chạm đúp hoặc bấm đúp để xoá các ô và tìm ra bức tranh giấu bên dưới.</t>
+          <t>Lái trực thăng bắt các đám mây theo đúng thứ tự.</t>
         </is>
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>Rèn kỹ năng phối hợp vận động.</t>
+          <t>Học thứ tự các số.</t>
         </is>
       </c>
       <c r="I150" s="9" t="inlineStr">
         <is>
-          <t>Tin học</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="J150" s="9" t="inlineStr">
         <is>
-          <t>NL tin học · NL công nghệ</t>
+          <t>NL tính toán · NL giải quyết vấn đề</t>
         </is>
       </c>
       <c r="K150" s="9" t="inlineStr">
         <is>
-          <t>5.1 Giải quyết vấn đề kỹ thuật — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L150" s="9" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="M150" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Rèn kỹ năng phối hợp vận động. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học thứ tự các số. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N150" s="9" t="inlineStr">
         <is>
-          <t>Bàn phím cũ tháo rời cho trẻ sờ và gọi tên phím.</t>
+          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
         </is>
       </c>
     </row>
@@ -10978,17 +10978,17 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>Chỉ đúng người thân</t>
+          <t>Chạm đúp hoặc bấm đúp</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>family_find_relative</t>
+          <t>erase_2clic</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Khoa học</t>
+          <t>Máy tính</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
@@ -11003,27 +11003,27 @@
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Chọn hai người có quan hệ họ hàng được nêu.</t>
+          <t>Chạm đúp hoặc bấm đúp để xoá các ô và tìm ra bức tranh giấu bên dưới.</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>Học các mối quan hệ trong gia đình, theo hệ tuyến tính dùng ở phần lớn xã hội phương Tây.</t>
+          <t>Rèn kỹ năng phối hợp vận động.</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử và Địa lí</t>
+          <t>Tin học</t>
         </is>
       </c>
       <c r="J151" s="7" t="inlineStr">
         <is>
-          <t>NL tìm hiểu xã hội · NL khoa học</t>
+          <t>NL tin học · NL công nghệ</t>
         </is>
       </c>
       <c r="K151" s="7" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>5.1 Giải quyết vấn đề kỹ thuật — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L151" s="7" t="inlineStr">
@@ -11033,12 +11033,12 @@
       </c>
       <c r="M151" s="7" t="inlineStr">
         <is>
-          <t>CẨN THẬN: cùng vấn đề xưng hô như hoạt động Gia đình. Chưa nên dùng để dạy.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Rèn kỹ năng phối hợp vận động. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N151" s="7" t="inlineStr">
         <is>
-          <t>Dòng thời gian bằng dây và kẹp ảnh treo ngang lớp.</t>
+          <t>Bàn phím cũ tháo rời cho trẻ sờ và gọi tên phím.</t>
         </is>
       </c>
     </row>
@@ -11048,17 +11048,17 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>Chữ cái nằm trong từ nào</t>
+          <t>Chỉ đúng người thân</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>letter-in-word</t>
+          <t>family_find_relative</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>Đọc</t>
+          <t>Khoa học</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
@@ -11073,27 +11073,27 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>Tìm những từ có chứa chữ cái đã cho.</t>
+          <t>Chọn hai người có quan hệ họ hàng được nêu.</t>
         </is>
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>Luyện tìm một chữ cái cho trước trong các từ.</t>
+          <t>Học các mối quan hệ trong gia đình, theo hệ tuyến tính dùng ở phần lớn xã hội phương Tây.</t>
         </is>
       </c>
       <c r="I152" s="9" t="inlineStr">
         <is>
-          <t>Tiếng Việt</t>
+          <t>Lịch sử và Địa lí</t>
         </is>
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>NL ngôn ngữ · NL giao tiếp</t>
+          <t>NL tìm hiểu xã hội · NL khoa học</t>
         </is>
       </c>
       <c r="K152" s="9" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L152" s="9" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="M152" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Luyện tìm một chữ cái cho trước trong các từ. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>CẨN THẬN: cùng vấn đề xưng hô như hoạt động Gia đình. Chưa nên dùng để dạy.</t>
         </is>
       </c>
       <c r="N152" s="9" t="inlineStr">
         <is>
-          <t>Thẻ chữ và tranh, ghép trên bàn.</t>
+          <t>Dòng thời gian bằng dây và kẹp ảnh treo ngang lớp.</t>
         </is>
       </c>
     </row>
@@ -11118,17 +11118,17 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>Chữ cái rơi</t>
+          <t>Chữ cái nằm trong từ nào</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>gletters</t>
+          <t>letter-in-word</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Máy tính</t>
+          <t>Đọc</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
@@ -11143,12 +11143,12 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Gõ các chữ cái đang rơi trước khi chúng chạm đất.</t>
+          <t>Tìm những từ có chứa chữ cái đã cho.</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>Ghép chữ cái trên bàn phím với chữ cái trên màn hình.</t>
+          <t>Luyện tìm một chữ cái cho trước trong các từ.</t>
         </is>
       </c>
       <c r="I153" s="7" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="K153" s="7" t="inlineStr">
         <is>
-          <t>5.1 Giải quyết vấn đề kỹ thuật — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L153" s="7" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="M153" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Ghép chữ cái trên bàn phím với chữ cái trên màn hình. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Luyện tìm một chữ cái cho trước trong các từ. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N153" s="7" t="inlineStr">
         <is>
-          <t>Thẻ chữ cắt rời, ghép trên bàn.</t>
+          <t>Thẻ chữ và tranh, ghép trên bàn.</t>
         </is>
       </c>
     </row>
@@ -11188,17 +11188,17 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>Gia đình</t>
+          <t>Chữ cái rơi</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>gletters</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Khoa học</t>
+          <t>Máy tính</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
@@ -11213,27 +11213,27 @@
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>Chọn cách gọi đúng cho người thân này trong gia đình.</t>
+          <t>Gõ các chữ cái đang rơi trước khi chúng chạm đất.</t>
         </is>
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>Học các mối quan hệ trong gia đình, theo hệ tuyến tính dùng ở phần lớn xã hội phương Tây.</t>
+          <t>Ghép chữ cái trên bàn phím với chữ cái trên màn hình.</t>
         </is>
       </c>
       <c r="I154" s="9" t="inlineStr">
         <is>
-          <t>Lịch sử và Địa lí</t>
+          <t>Tiếng Việt</t>
         </is>
       </c>
       <c r="J154" s="9" t="inlineStr">
         <is>
-          <t>NL tìm hiểu xã hội · NL khoa học</t>
+          <t>NL ngôn ngữ · NL giao tiếp</t>
         </is>
       </c>
       <c r="K154" s="9" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>5.1 Giải quyết vấn đề kỹ thuật — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L154" s="9" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="M154" s="9" t="inlineStr">
         <is>
-          <t>CẨN THẬN: cây gia đình gốc theo lối phương Tây, chỉ có một ô 'chú/bác/cậu'. Đọc sheet CanThietKeLai trước khi dùng trong lớp.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Ghép chữ cái trên bàn phím với chữ cái trên màn hình. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
         <is>
-          <t>Dòng thời gian bằng dây và kẹp ảnh treo ngang lớp.</t>
+          <t>Thẻ chữ cắt rời, ghép trên bàn.</t>
         </is>
       </c>
     </row>
@@ -11258,17 +11258,17 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>Giai điệu</t>
+          <t>Gia đình</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>melody</t>
+          <t>family</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Khám phá</t>
+          <t>Khoa học</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
@@ -11283,22 +11283,22 @@
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Lặp lại một chuỗi âm thanh.</t>
+          <t>Chọn cách gọi đúng cho người thân này trong gia đình.</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>Hoạt động rèn tai nghe.</t>
+          <t>Học các mối quan hệ trong gia đình, theo hệ tuyến tính dùng ở phần lớn xã hội phương Tây.</t>
         </is>
       </c>
       <c r="I155" s="7" t="inlineStr">
         <is>
-          <t>Âm nhạc</t>
+          <t>Lịch sử và Địa lí</t>
         </is>
       </c>
       <c r="J155" s="7" t="inlineStr">
         <is>
-          <t>NL thẩm mĩ · NL cảm thụ âm nhạc</t>
+          <t>NL tìm hiểu xã hội · NL khoa học</t>
         </is>
       </c>
       <c r="K155" s="7" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="M155" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Hoạt động rèn tai nghe. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>CẨN THẬN: cây gia đình gốc theo lối phương Tây, chỉ có một ô 'chú/bác/cậu'. Đọc sheet CanThietKeLai trước khi dùng trong lớp.</t>
         </is>
       </c>
       <c r="N155" s="7" t="inlineStr">
         <is>
-          <t>Bộ chai nước gõ theo cao độ.</t>
+          <t>Dòng thời gian bằng dây và kẹp ảnh treo ngang lớp.</t>
         </is>
       </c>
     </row>
@@ -11328,17 +11328,17 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>Học phép cộng</t>
+          <t>Giai điệu</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>learn_additions</t>
+          <t>melody</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Khám phá</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
@@ -11353,27 +11353,27 @@
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>Học phép cộng với các số nhỏ.</t>
+          <t>Lặp lại một chuỗi âm thanh.</t>
         </is>
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
-          <t>Học phép cộng bằng cách cộng số lượng.</t>
+          <t>Hoạt động rèn tai nghe.</t>
         </is>
       </c>
       <c r="I156" s="9" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Âm nhạc</t>
         </is>
       </c>
       <c r="J156" s="9" t="inlineStr">
         <is>
-          <t>NL tính toán · NL giải quyết vấn đề</t>
+          <t>NL thẩm mĩ · NL cảm thụ âm nhạc</t>
         </is>
       </c>
       <c r="K156" s="9" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L156" s="9" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="M156" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học phép cộng bằng cách cộng số lượng. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Hoạt động rèn tai nghe. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N156" s="9" t="inlineStr">
         <is>
-          <t>Que tính, hạt, nắp chai — làm phép tính bằng tay trước.</t>
+          <t>Bộ chai nước gõ theo cao độ.</t>
         </is>
       </c>
     </row>
@@ -11398,12 +11398,12 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>Học phép trừ</t>
+          <t>Học phép cộng</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>learn_subtractions</t>
+          <t>learn_additions</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Học phép trừ với các số nhỏ.</t>
+          <t>Học phép cộng với các số nhỏ.</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>Học phép trừ bằng cách đếm kết quả.</t>
+          <t>Học phép cộng bằng cách cộng số lượng.</t>
         </is>
       </c>
       <c r="I157" s="7" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="M157" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học phép trừ bằng cách đếm kết quả. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học phép cộng bằng cách cộng số lượng. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N157" s="7" t="inlineStr">
@@ -11468,17 +11468,17 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>Khám phá vật nuôi trong trang trại</t>
+          <t>Học phép trừ</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>explore_farm_animals</t>
+          <t>learn_subtractions</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>Khoa học</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
@@ -11493,27 +11493,27 @@
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>Tìm hiểu vật nuôi trong trang trại, tiếng kêu của chúng và những điều thú vị.</t>
+          <t>Học phép trừ với các số nhỏ.</t>
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
-          <t>Học cách gắn tiếng kêu của con vật với tên gọi và hình dáng của nó.</t>
+          <t>Học phép trừ bằng cách đếm kết quả.</t>
         </is>
       </c>
       <c r="I158" s="9" t="inlineStr">
         <is>
-          <t>Tự nhiên và Xã hội (TH) · Khoa học · KHTN</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>NL khoa học · NL tìm hiểu tự nhiên</t>
+          <t>NL tính toán · NL giải quyết vấn đề</t>
         </is>
       </c>
       <c r="K158" s="9" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L158" s="9" t="inlineStr">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="M158" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học cách gắn tiếng kêu của con vật với tên gọi và hình dáng của nó. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học phép trừ bằng cách đếm kết quả. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Que tính, hạt, nắp chai — làm phép tính bằng tay trước.</t>
         </is>
       </c>
     </row>
@@ -11538,17 +11538,17 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>Luyện cộng bằng trò bắn bia</t>
+          <t>Khám phá vật nuôi trong trang trại</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>explore_farm_animals</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Khoa học</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
@@ -11563,27 +11563,27 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Ném phi tiêu vào bia rồi tính điểm của con.</t>
+          <t>Tìm hiểu vật nuôi trong trang trại, tiếng kêu của chúng và những điều thú vị.</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>Luyện cộng nhiều số.</t>
+          <t>Học cách gắn tiếng kêu của con vật với tên gọi và hình dáng của nó.</t>
         </is>
       </c>
       <c r="I159" s="7" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Tự nhiên và Xã hội (TH) · Khoa học · KHTN</t>
         </is>
       </c>
       <c r="J159" s="7" t="inlineStr">
         <is>
-          <t>NL tính toán · NL giải quyết vấn đề</t>
+          <t>NL khoa học · NL tìm hiểu tự nhiên</t>
         </is>
       </c>
       <c r="K159" s="7" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L159" s="7" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="M159" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Luyện cộng nhiều số. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học cách gắn tiếng kêu của con vật với tên gọi và hình dáng của nó. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N159" s="7" t="inlineStr">
         <is>
-          <t>Que tính, hạt, nắp chai — làm phép tính bằng tay trước.</t>
+          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
         </is>
       </c>
     </row>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>Mũ ảo thuật (phép cộng)</t>
+          <t>Luyện cộng bằng trò bắn bia</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>magic-hat-plus</t>
+          <t>target</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>Đếm xem có bao nhiêu ngôi sao dưới chiếc mũ ảo thuật.</t>
+          <t>Ném phi tiêu vào bia rồi tính điểm của con.</t>
         </is>
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
-          <t>Học phép cộng.</t>
+          <t>Luyện cộng nhiều số.</t>
         </is>
       </c>
       <c r="I160" s="9" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="M160" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học phép cộng. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Luyện cộng nhiều số. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N160" s="9" t="inlineStr">
@@ -11678,12 +11678,12 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>Mũ ảo thuật (phép trừ)</t>
+          <t>Mũ ảo thuật (phép cộng)</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>magic-hat-minus</t>
+          <t>magic-hat-plus</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Tính xem có bao nhiêu ngôi sao dưới chiếc mũ ảo thuật.</t>
+          <t>Đếm xem có bao nhiêu ngôi sao dưới chiếc mũ ảo thuật.</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>Học phép trừ.</t>
+          <t>Học phép cộng.</t>
         </is>
       </c>
       <c r="I161" s="7" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M161" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học phép trừ. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học phép cộng. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N161" s="7" t="inlineStr">
@@ -11748,12 +11748,12 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>Nối số theo thứ tự</t>
+          <t>Mũ ảo thuật (phép trừ)</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>number_sequence</t>
+          <t>magic-hat-minus</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>Chọn lần lượt các số theo đúng dãy số.</t>
+          <t>Tính xem có bao nhiêu ngôi sao dưới chiếc mũ ảo thuật.</t>
         </is>
       </c>
       <c r="H162" s="9" t="inlineStr">
         <is>
-          <t>Học dãy số theo thứ tự.</t>
+          <t>Học phép trừ.</t>
         </is>
       </c>
       <c r="I162" s="9" t="inlineStr">
@@ -11803,12 +11803,12 @@
       </c>
       <c r="M162" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học dãy số theo thứ tự. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học phép trừ. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N162" s="9" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Que tính, hạt, nắp chai — làm phép tính bằng tay trước.</t>
         </is>
       </c>
     </row>
@@ -11818,17 +11818,17 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>Phân biệt tay trái, tay phải</t>
+          <t>Nối số theo thứ tự</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>leftright</t>
+          <t>number_sequence</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Xếp hình</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr">
@@ -11843,22 +11843,22 @@
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Xác định xem đó là bàn tay phải hay bàn tay trái.</t>
+          <t>Chọn lần lượt các số theo đúng dãy số.</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>Phân biệt tay phải và tay trái từ nhiều góc nhìn. Biểu diễn không gian.</t>
+          <t>Học dãy số theo thứ tự.</t>
         </is>
       </c>
       <c r="I163" s="7" t="inlineStr">
         <is>
-          <t>Hoạt động trải nghiệm</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="J163" s="7" t="inlineStr">
         <is>
-          <t>NL tự chủ và tự học · NL giải quyết vấn đề</t>
+          <t>NL tính toán · NL giải quyết vấn đề</t>
         </is>
       </c>
       <c r="K163" s="7" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="M163" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Phân biệt tay phải và tay trái từ nhiều góc nhìn. Biểu diễn không gian. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học dãy số theo thứ tự. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N163" s="7" t="inlineStr">
         <is>
-          <t>Bộ xếp hình cắt từ bìa.</t>
+          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
         </is>
       </c>
     </row>
@@ -11888,17 +11888,17 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>So sánh số</t>
+          <t>Phân biệt tay trái, tay phải</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>comparator</t>
+          <t>leftright</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Xếp hình</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
@@ -11913,22 +11913,22 @@
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>So sánh hai số rồi chọn dấu thích hợp.</t>
+          <t>Xác định xem đó là bàn tay phải hay bàn tay trái.</t>
         </is>
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
-          <t>Học cách so sánh giá trị của các số.</t>
+          <t>Phân biệt tay phải và tay trái từ nhiều góc nhìn. Biểu diễn không gian.</t>
         </is>
       </c>
       <c r="I164" s="9" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Hoạt động trải nghiệm</t>
         </is>
       </c>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>NL tính toán · NL giải quyết vấn đề</t>
+          <t>NL tự chủ và tự học · NL giải quyết vấn đề</t>
         </is>
       </c>
       <c r="K164" s="9" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="M164" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học cách so sánh giá trị của các số. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Phân biệt tay phải và tay trái từ nhiều góc nhìn. Biểu diễn không gian. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N164" s="9" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Bộ xếp hình cắt từ bìa.</t>
         </is>
       </c>
     </row>
@@ -11958,17 +11958,17 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>Sắp chữ cái theo thứ tự</t>
+          <t>So sánh số</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>ordering_alphabets</t>
+          <t>comparator</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Đọc</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
@@ -11983,22 +11983,22 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Sắp các chữ cái đã cho theo thứ tự bảng chữ cái, xuôi hoặc ngược theo yêu cầu.</t>
+          <t>So sánh hai số rồi chọn dấu thích hợp.</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>Học thứ tự bảng chữ cái.</t>
+          <t>Học cách so sánh giá trị của các số.</t>
         </is>
       </c>
       <c r="I165" s="7" t="inlineStr">
         <is>
-          <t>Tiếng Việt</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="J165" s="7" t="inlineStr">
         <is>
-          <t>NL ngôn ngữ · NL giao tiếp</t>
+          <t>NL tính toán · NL giải quyết vấn đề</t>
         </is>
       </c>
       <c r="K165" s="7" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="M165" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học thứ tự bảng chữ cái. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học cách so sánh giá trị của các số. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N165" s="7" t="inlineStr">
         <is>
-          <t>Thẻ chữ cắt rời, ghép trên bàn.</t>
+          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
         </is>
       </c>
     </row>
@@ -12028,12 +12028,12 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>Sắp câu cho đúng</t>
+          <t>Sắp chữ cái theo thứ tự</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>ordering_sentences</t>
+          <t>ordering_alphabets</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>Sắp các từ đã cho thành một câu có nghĩa.</t>
+          <t>Sắp các chữ cái đã cho theo thứ tự bảng chữ cái, xuôi hoặc ngược theo yêu cầu.</t>
         </is>
       </c>
       <c r="H166" s="9" t="inlineStr">
         <is>
-          <t>Luyện sắp từ thành một câu có nghĩa.</t>
+          <t>Học thứ tự bảng chữ cái.</t>
         </is>
       </c>
       <c r="I166" s="9" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="M166" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Luyện sắp từ thành một câu có nghĩa. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học thứ tự bảng chữ cái. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N166" s="9" t="inlineStr">
         <is>
-          <t>Thẻ chữ và tranh, ghép trên bàn.</t>
+          <t>Thẻ chữ cắt rời, ghép trên bàn.</t>
         </is>
       </c>
     </row>
@@ -12098,17 +12098,17 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>Sắp số theo thứ tự</t>
+          <t>Sắp câu cho đúng</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>ordering_numbers</t>
+          <t>ordering_sentences</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Đọc</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr">
@@ -12123,22 +12123,22 @@
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Sắp các số đã cho theo thứ tự tăng dần hoặc giảm dần theo yêu cầu.</t>
+          <t>Sắp các từ đã cho thành một câu có nghĩa.</t>
         </is>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>Luyện sắp số theo thứ tự.</t>
+          <t>Luyện sắp từ thành một câu có nghĩa.</t>
         </is>
       </c>
       <c r="I167" s="7" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Tiếng Việt</t>
         </is>
       </c>
       <c r="J167" s="7" t="inlineStr">
         <is>
-          <t>NL tính toán · NL giải quyết vấn đề</t>
+          <t>NL ngôn ngữ · NL giao tiếp</t>
         </is>
       </c>
       <c r="K167" s="7" t="inlineStr">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="M167" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Luyện sắp số theo thứ tự. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Luyện sắp từ thành một câu có nghĩa. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N167" s="7" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Thẻ chữ và tranh, ghép trên bàn.</t>
         </is>
       </c>
     </row>
@@ -12168,17 +12168,17 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>Sắp sự kiện theo thời gian</t>
+          <t>Sắp số theo thứ tự</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>ordering_chronology</t>
+          <t>ordering_numbers</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Khám phá</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
@@ -12193,27 +12193,27 @@
       </c>
       <c r="G168" s="9" t="inlineStr">
         <is>
-          <t>Sắp các sự kiện đã cho theo thứ tự thời gian.</t>
+          <t>Sắp các số đã cho theo thứ tự tăng dần hoặc giảm dần theo yêu cầu.</t>
         </is>
       </c>
       <c r="H168" s="9" t="inlineStr">
         <is>
-          <t>Học cách sắp một chuỗi sự kiện theo thứ tự thời gian.</t>
+          <t>Luyện sắp số theo thứ tự.</t>
         </is>
       </c>
       <c r="I168" s="9" t="inlineStr">
         <is>
-          <t>Hoạt động trải nghiệm</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="J168" s="9" t="inlineStr">
         <is>
-          <t>NL tự chủ và tự học · NL giải quyết vấn đề</t>
+          <t>NL tính toán · NL giải quyết vấn đề</t>
         </is>
       </c>
       <c r="K168" s="9" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L168" s="9" t="inlineStr">
@@ -12223,12 +12223,12 @@
       </c>
       <c r="M168" s="9" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học cách sắp một chuỗi sự kiện theo thứ tự thời gian. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Luyện sắp số theo thứ tự. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N168" s="9" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
         </is>
       </c>
     </row>
@@ -12238,17 +12238,17 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>Sắp theo thứ tự số</t>
+          <t>Sắp sự kiện theo thời gian</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>planegame</t>
+          <t>ordering_chronology</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Khám phá</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr">
@@ -12263,27 +12263,27 @@
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Lái trực thăng bắt các đám mây theo đúng thứ tự.</t>
+          <t>Sắp các sự kiện đã cho theo thứ tự thời gian.</t>
         </is>
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>Học thứ tự các số.</t>
+          <t>Học cách sắp một chuỗi sự kiện theo thứ tự thời gian.</t>
         </is>
       </c>
       <c r="I169" s="7" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Hoạt động trải nghiệm</t>
         </is>
       </c>
       <c r="J169" s="7" t="inlineStr">
         <is>
-          <t>NL tính toán · NL giải quyết vấn đề</t>
+          <t>NL tự chủ và tự học · NL giải quyết vấn đề</t>
         </is>
       </c>
       <c r="K169" s="7" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu — Ở mức làm quen thiết bị và thao tác số cơ bản, bậc 1 của khung.</t>
         </is>
       </c>
       <c r="L169" s="7" t="inlineStr">
@@ -12293,12 +12293,12 @@
       </c>
       <c r="M169" s="7" t="inlineStr">
         <is>
-          <t>Luyện tập: máy hỏi – trẻ đáp. Học thứ tự các số. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
+          <t>Luyện tập: máy hỏi – trẻ đáp. Học cách sắp một chuỗi sự kiện theo thứ tự thời gian. Giữ tối đa 10 phút rồi nối sang việc làm tay.</t>
         </is>
       </c>
       <c r="N169" s="7" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Vật thật xếp theo quy luật trên bàn.</t>
         </is>
       </c>
     </row>
